--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/GUARNICAO CARBURADOR.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/GUARNICAO CARBURADOR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +492,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,11 +512,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -551,11 +530,6 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
